--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486707_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486707_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. SOLE MOURATAY</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5377</v>
+        <v>4.0331</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3345</v>
+        <v>0.9608</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2032</v>
+        <v>3.0723</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8625</v>
+        <v>3.4499</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1314</v>
+        <v>1.5102</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.9939</v>
+        <v>1.9397</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6216</v>
+        <v>2.2022</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9599</v>
+        <v>1.0967</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.3383</v>
+        <v>1.1056</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4841</v>
+        <v>1.2477</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8285</v>
+        <v>0.4135</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.8341</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4235</v>
+        <v>0.0965</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1303</v>
+        <v>-0.083</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2931</v>
+        <v>0.1795</v>
       </c>
       <c r="V2" t="n">
-        <v>3.3975</v>
+        <v>-0.2856</v>
       </c>
       <c r="W2" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9736</v>
+        <v>4.0314</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7549</v>
+        <v>1.9618</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2186</v>
+        <v>2.0696</v>
       </c>
       <c r="G3" t="n">
         <v>3.9401</v>
@@ -688,13 +688,13 @@
         <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.623</v>
+        <v>-0.5652</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3863</v>
+        <v>-0.1794</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2367</v>
+        <v>-0.3857</v>
       </c>
       <c r="V3" t="n">
         <v>0.6565</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>M. SOLE MOURATAY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3989</v>
+        <v>3.1143</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5443</v>
+        <v>2.5071</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8546</v>
+        <v>0.6072</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6611</v>
+        <v>-0.8625</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3455</v>
+        <v>1.1314</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3157</v>
+        <v>-1.9939</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8548</v>
+        <v>0.6216</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5527</v>
+        <v>1.9599</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3022</v>
+        <v>-1.3383</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1937</v>
+        <v>-1.4841</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2072</v>
+        <v>-0.8285</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0135</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7997</v>
+        <v>0.0001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7168</v>
+        <v>0.303</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0829</v>
+        <v>-0.3028</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0273</v>
+        <v>3.3975</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.0273</v>
+        <v>2.741</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>D. MARTINEZ DE LA SERNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3463</v>
+        <v>3.0599</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5471</v>
+        <v>1.0292</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7992</v>
+        <v>2.0307</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4499</v>
+        <v>3.3081</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5102</v>
+        <v>1.303</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9397</v>
+        <v>2.0052</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2022</v>
+        <v>2.3988</v>
       </c>
       <c r="K5" t="n">
         <v>1.0967</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1056</v>
+        <v>1.3022</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2477</v>
+        <v>0.9093</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4135</v>
+        <v>0.2063</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8341</v>
+        <v>0.703</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>-1.3515</v>
       </c>
       <c r="R5" t="n">
         <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5903</v>
+        <v>-0.8274</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4966</v>
+        <v>-0.3037</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.5238</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2856</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ BRUNO</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6941</v>
+        <v>2.9025</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6265</v>
+        <v>1.9238</v>
       </c>
       <c r="F6" t="n">
-        <v>4.3207</v>
+        <v>0.9787</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1061</v>
+        <v>2.6611</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5167</v>
+        <v>1.3455</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4106</v>
+        <v>1.3157</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.1812</v>
+        <v>2.8548</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.3439</v>
+        <v>1.5527</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1628</v>
+        <v>1.3022</v>
       </c>
       <c r="M6" t="n">
-        <v>2.075</v>
+        <v>-0.1937</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8272</v>
+        <v>-0.2072</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2478</v>
+        <v>0.0135</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2869</v>
+        <v>0.3033</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0279</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3148</v>
+        <v>0.2071</v>
       </c>
       <c r="V6" t="n">
-        <v>2.741</v>
+        <v>-1.0273</v>
       </c>
       <c r="W6" t="n">
-        <v>2.741</v>
+        <v>-1.0273</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MARTINEZ DE LA SERNA</t>
+          <t>J. MARTÍNEZ BRUNO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2986</v>
+        <v>2.3383</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6155</v>
+        <v>-1.8334</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6831</v>
+        <v>4.1717</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3081</v>
+        <v>-1.1061</v>
       </c>
       <c r="H7" t="n">
-        <v>1.303</v>
+        <v>-2.5167</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0052</v>
+        <v>1.4106</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3988</v>
+        <v>-3.1812</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0967</v>
+        <v>-3.3439</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3022</v>
+        <v>0.1628</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9093</v>
+        <v>2.075</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2063</v>
+        <v>0.8272</v>
       </c>
       <c r="O7" t="n">
-        <v>0.703</v>
+        <v>1.2478</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3515</v>
+        <v>-1.1585</v>
       </c>
       <c r="R7" t="n">
         <v>1.9308</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5888</v>
+        <v>-0.0689</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7174</v>
+        <v>-0.2347</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8714</v>
+        <v>0.1658</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.741</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2856</v>
+        <v>2.741</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>M. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8333</v>
+        <v>1.5686</v>
       </c>
       <c r="E8" t="n">
-        <v>0.51</v>
+        <v>1.331</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3233</v>
+        <v>0.2376</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3458</v>
+        <v>1.8544</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9931</v>
+        <v>0.5522</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3527</v>
+        <v>1.3022</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4692</v>
+        <v>1.6968</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5099</v>
+        <v>0.5528</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0407</v>
+        <v>1.144</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8766</v>
+        <v>0.1576</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4832</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3934</v>
+        <v>0.1582</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0992</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1377</v>
+        <v>-0.3658</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2369</v>
+        <v>-0.5651</v>
       </c>
       <c r="V8" t="n">
-        <v>1.9268</v>
+        <v>-0.8995</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6991000000000001</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8861</v>
+        <v>1.4775</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1326</v>
+        <v>0.3032</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2465</v>
+        <v>1.1744</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7498</v>
+        <v>-1.3458</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2412</v>
+        <v>-0.9931</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5086000000000001</v>
+        <v>-0.3527</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1507</v>
+        <v>-0.4692</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0694</v>
+        <v>-0.5099</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0814</v>
+        <v>0.0407</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4009</v>
+        <v>-0.8766</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8282</v>
+        <v>-0.4832</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4272</v>
+        <v>-0.3934</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.3862</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1585</v>
+        <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4083</v>
+        <v>-0.455</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3038</v>
+        <v>-0.0692</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1045</v>
+        <v>-0.3859</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6138</v>
+        <v>1.9268</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8995</v>
+        <v>0.6991000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. YOUNG MEDIERO</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7287</v>
+        <v>0.8323</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8139</v>
+        <v>1.0291</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0852</v>
+        <v>-0.1968</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8544</v>
+        <v>0.7498</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5522</v>
+        <v>0.2412</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3022</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6968</v>
+        <v>1.1507</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5528</v>
+        <v>1.0694</v>
       </c>
       <c r="L10" t="n">
-        <v>1.144</v>
+        <v>0.0814</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1576</v>
+        <v>-0.4009</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.8282</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1582</v>
+        <v>0.4272</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7709</v>
+        <v>-0.4621</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8829</v>
+        <v>-0.4072</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.888</v>
+        <v>-0.0549</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8995</v>
+        <v>-0.6138</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X10" t="n">
         <v>-0.8995</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6241</v>
+        <v>-1.256</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1049</v>
+        <v>-2.5103</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4808</v>
+        <v>1.2543</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0917</v>
+        <v>1.3504</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.641</v>
+        <v>2.0694</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5493</v>
+        <v>-0.7189</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5531</v>
+        <v>1.6688</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.6751</v>
+        <v>2.2769</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1221</v>
+        <v>-0.6081</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4614</v>
+        <v>-0.3184</v>
       </c>
       <c r="N11" t="n">
-        <v>1.0341</v>
+        <v>-0.2075</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4272</v>
+        <v>-0.1108</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6953</v>
+        <v>-0.4826</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4136</v>
+        <v>-0.3176</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2817</v>
+        <v>-0.1651</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7772</v>
+        <v>-1.9262</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1308</v>
+        <v>-3.2083</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3536</v>
+        <v>1.2821</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3504</v>
+        <v>-1.0917</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0694</v>
+        <v>-1.641</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7189</v>
+        <v>0.5493</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6688</v>
+        <v>-2.5531</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2769</v>
+        <v>-2.6751</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6081</v>
+        <v>0.1221</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3184</v>
+        <v>1.4614</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2075</v>
+        <v>1.0341</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1108</v>
+        <v>0.4272</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0038</v>
+        <v>0.3932</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9381</v>
+        <v>0.3101</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4768</v>
+        <v>-4.3567</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3007</v>
+        <v>-3.4042</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1761</v>
+        <v>-0.9526</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1843</v>
@@ -1468,13 +1468,13 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2579</v>
+        <v>-1.1378</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0279</v>
+        <v>-0.1313</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.23</v>
+        <v>-1.0065</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2277</v>
@@ -1501,37 +1501,37 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.8192</v>
+        <v>15.819</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08990000000000009</v>
+        <v>0.08980000000000032</v>
       </c>
       <c r="F14" t="n">
-        <v>15.7293</v>
+        <v>15.7292</v>
       </c>
       <c r="G14" t="n">
         <v>10.7234</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7948</v>
+        <v>3.794800000000001</v>
       </c>
       <c r="I14" t="n">
         <v>6.9288</v>
       </c>
       <c r="J14" t="n">
-        <v>7.768600000000001</v>
+        <v>7.768599999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>3.801199999999999</v>
+        <v>3.801199999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>3.968</v>
+        <v>3.968000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>2.9547</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.006400000000000072</v>
+        <v>-0.006399999999999961</v>
       </c>
       <c r="O14" t="n">
         <v>2.9607</v>
@@ -1546,16 +1546,16 @@
         <v>18.3425</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.1368</v>
+        <v>-4.136799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3825</v>
+        <v>-1.3826</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.7544</v>
+        <v>-2.7543</v>
       </c>
       <c r="V14" t="n">
-        <v>3.440200000000001</v>
+        <v>3.440199999999999</v>
       </c>
       <c r="W14" t="n">
         <v>6.2536</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6825</v>
+        <v>2.4184</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0984</v>
+        <v>1.1287</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7809</v>
+        <v>1.2897</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7401</v>
+        <v>1.4447</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2207</v>
+        <v>0.1854</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9608</v>
+        <v>1.2593</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8977000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3303</v>
+        <v>1.1521</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5674</v>
+        <v>1.1078</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1576</v>
+        <v>-0.8152</v>
       </c>
       <c r="N15" t="n">
-        <v>0.551</v>
+        <v>-0.9667</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3934</v>
+        <v>0.1514</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1585</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5497</v>
+        <v>0.0895</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7646</v>
+        <v>0.1857</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2149</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2856</v>
+        <v>1.2703</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.3599</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.719</v>
       </c>
       <c r="F16" t="n">
-        <v>1.495</v>
+        <v>2.0789</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9385</v>
+        <v>-0.7401</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3039</v>
+        <v>0.2207</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3654</v>
+        <v>-0.9608</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0771</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2681</v>
+        <v>-0.3303</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3451</v>
+        <v>-0.5674</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0156</v>
+        <v>0.1576</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0359</v>
+        <v>0.551</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0203</v>
+        <v>-0.3934</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1585</v>
+        <v>1.1585</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5499</v>
+        <v>1.2272</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4335</v>
+        <v>1.1441</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1164</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5133</v>
+        <v>-0.2856</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8568</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5524</v>
+        <v>0.0024</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2158</v>
+        <v>-1.6664</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7682</v>
+        <v>1.6688</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4447</v>
+        <v>-0.9385</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1854</v>
+        <v>-2.3039</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2593</v>
+        <v>1.3654</v>
       </c>
       <c r="J17" t="n">
-        <v>2.26</v>
+        <v>0.0771</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1521</v>
+        <v>-1.2681</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1078</v>
+        <v>1.3451</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8152</v>
+        <v>-1.0156</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9667</v>
+        <v>-1.0359</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1514</v>
+        <v>0.0203</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3862</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7764</v>
+        <v>0.5861</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1588</v>
+        <v>0.2959</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6176</v>
+        <v>0.2902</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2703</v>
+        <v>1.5133</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6138</v>
+        <v>0.8568</v>
       </c>
       <c r="X17" t="n">
         <v>0.6565</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.145</v>
+        <v>-1.4758</v>
       </c>
       <c r="E18" t="n">
-        <v>0.453</v>
+        <v>-1.6618</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.598</v>
+        <v>0.1861</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2988</v>
+        <v>-1.3033</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0757</v>
+        <v>-0.2069</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3745</v>
+        <v>-1.0964</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4399</v>
+        <v>-1.379</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0073</v>
+        <v>-0.6895</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5674</v>
+        <v>-0.6895</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7387</v>
+        <v>0.0756</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0684</v>
+        <v>0.4826</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8071</v>
+        <v>-0.4069</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6018</v>
+        <v>-0.3655</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5851</v>
+        <v>-0.2829</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0168</v>
+        <v>-0.0827</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.8689</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.6412</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5295</v>
+        <v>-2.1216</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7652</v>
+        <v>-1.3626</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2357</v>
+        <v>-0.7591</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3033</v>
+        <v>-0.6046</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2069</v>
+        <v>-0.7176</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0964</v>
+        <v>0.113</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.379</v>
+        <v>0.6925</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6895</v>
+        <v>0.0414</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6895</v>
+        <v>0.6511</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0756</v>
+        <v>-1.297</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4826</v>
+        <v>-0.759</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4069</v>
+        <v>-0.5381</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1931</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4193</v>
+        <v>0.0276</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3863</v>
+        <v>-0.1242</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.033</v>
+        <v>0.1518</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7479</v>
+        <v>-2.224</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9849</v>
+        <v>-0.4678</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7629</v>
+        <v>-1.7562</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9194</v>
@@ -2014,13 +2014,13 @@
         <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1795</v>
+        <v>1.7033</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2201</v>
+        <v>0.7372</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9594</v>
+        <v>0.9661</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2703</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5023</v>
+        <v>-2.2921</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5694</v>
+        <v>-1.7189</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9329</v>
+        <v>-0.5732</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6046</v>
+        <v>-0.2988</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7176</v>
+        <v>1.0757</v>
       </c>
       <c r="I21" t="n">
-        <v>0.113</v>
+        <v>-1.3745</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6925</v>
+        <v>0.4399</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0414</v>
+        <v>1.0073</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6511</v>
+        <v>-0.5674</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.297</v>
+        <v>-0.7387</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.759</v>
+        <v>0.0684</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5381</v>
+        <v>-0.8071</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5446</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3531</v>
+        <v>1.4548</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3311</v>
+        <v>1.4132</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.022</v>
+        <v>0.0416</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.8689</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-1.6412</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="22">
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.776</v>
+        <v>-2.5691</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8279</v>
+        <v>-0.621</v>
       </c>
       <c r="F22" t="n">
         <v>-1.9481</v>
@@ -2170,10 +2170,10 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5792</v>
+        <v>-0.3724</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4415</v>
+        <v>-0.2346</v>
       </c>
       <c r="U22" t="n">
         <v>-0.1378</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1051</v>
+        <v>-2.8527</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9043</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2008</v>
+        <v>-2.0518</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4569</v>
@@ -2248,13 +2248,13 @@
         <v>0.3862</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7833</v>
+        <v>-0.5309</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.607</v>
+        <v>-0.5036</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1763</v>
+        <v>-0.0274</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2856</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2143</v>
+        <v>-6.0644</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.2875</v>
+        <v>-7.8396</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0732</v>
+        <v>1.7752</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6439</v>
@@ -2326,13 +2326,13 @@
         <v>2.1239</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8327</v>
+        <v>0.3172</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3244</v>
+        <v>0.1235</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4917</v>
+        <v>0.1937</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2362,10 +2362,10 @@
         <v>-15.819</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.7291</v>
+        <v>-15.7293</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.08970000000000011</v>
+        <v>-0.08970000000000056</v>
       </c>
       <c r="G25" t="n">
         <v>-10.7235</v>
@@ -2383,7 +2383,7 @@
         <v>0.006199999999999761</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.961</v>
+        <v>-2.961000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-7.768800000000001</v>
@@ -2392,7 +2392,7 @@
         <v>-3.8011</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.967900000000001</v>
+        <v>-3.9679</v>
       </c>
       <c r="P25" t="n">
         <v>-5.7923</v>
@@ -2407,10 +2407,10 @@
         <v>4.1369</v>
       </c>
       <c r="T25" t="n">
-        <v>2.754200000000001</v>
+        <v>2.7543</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3827</v>
+        <v>1.3824</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4401</v>
@@ -2419,7 +2419,7 @@
         <v>2.8134</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.2535</v>
+        <v>-6.253499999999999</v>
       </c>
     </row>
   </sheetData>
